--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:17</t>
+    <t xml:space="preserve">2026-09-09 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:12</t>
+    <t xml:space="preserve">2026-09-17 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:08</t>
+    <t xml:space="preserve">2026-09-23 12:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:37</t>
+    <t xml:space="preserve">2026-10-02 14:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:35</t>
+    <t xml:space="preserve">2026-10-04 09:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:05</t>
+    <t xml:space="preserve">2026-10-05 10:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -609,7 +609,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>527991.12</v>
+        <v>527991.13</v>
       </c>
     </row>
     <row r="4">
@@ -677,7 +677,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>462240.62</v>
+        <v>462240.63</v>
       </c>
     </row>
     <row r="8">
